--- a/SCRIPT_PDFS/SCRIPS_DOCUMENTADOS/PDF CALIDAD/IPS SIN MEDICION/indicadores sin medion.xlsx
+++ b/SCRIPT_PDFS/SCRIPS_DOCUMENTADOS/PDF CALIDAD/IPS SIN MEDICION/indicadores sin medion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SCRIPT PDFS\PDF CALIDAD\IPS SIN MEDICION\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Usuariios\prueba\Automatizaciones\SCRIPT_PDFS\SCRIPS_DOCUMENTADOS\PDF CALIDAD\IPS SIN MEDICION\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D912B751-4D28-4A10-8EB0-3403CC30FA54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A5E755E-66DE-4BDE-882C-12DFA3B7123B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{7F76B178-B5D4-4098-B7B9-F39AFCAC640C}"/>
+    <workbookView xWindow="1080" yWindow="1080" windowWidth="21600" windowHeight="11295" xr2:uid="{7F76B178-B5D4-4098-B7B9-F39AFCAC640C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="35">
   <si>
     <t>campoa</t>
   </si>
@@ -52,9 +52,6 @@
   </si>
   <si>
     <t>campod</t>
-  </si>
-  <si>
-    <t>campoe</t>
   </si>
   <si>
     <t>ADMINISTRADORA COUNTRY SAS</t>
@@ -90,19 +87,64 @@
     <t>NUEVA SALUD INTEGRAL IPS SAS</t>
   </si>
   <si>
-    <t>20.02.2026</t>
+    <t>0758-2021</t>
   </si>
   <si>
-    <t>ENERO 2026</t>
+    <t>0050-2024</t>
   </si>
   <si>
-    <t>ENERO</t>
+    <t>0726-2024</t>
   </si>
   <si>
-    <t>0508-2021</t>
+    <t>0890-2024</t>
   </si>
   <si>
-    <t>HOSPITAL SANTA BARBARA E.S.E.</t>
+    <t>0040-2025</t>
+  </si>
+  <si>
+    <t>0138-2025</t>
+  </si>
+  <si>
+    <t>0606-2025</t>
+  </si>
+  <si>
+    <t>0615-2025</t>
+  </si>
+  <si>
+    <t>0827-2021</t>
+  </si>
+  <si>
+    <t>GRUPO PREFERENCIAL SANAR IPS S.A.S.</t>
+  </si>
+  <si>
+    <t>CENTRO MEDICO DEPORTIVO MET SAS</t>
+  </si>
+  <si>
+    <t>IMÁGENES Y ESPECIALIDADES S.A.S. – IMESS S.A.S</t>
+  </si>
+  <si>
+    <t>EMPRESA SOCIAL DEL ESTADO HOSPITAL MUNICIPAL DE EL DORADO</t>
+  </si>
+  <si>
+    <t>E.S.E HOSPITAL HABACUC CALDERON CARMEN DE CARUPA</t>
+  </si>
+  <si>
+    <t>UNIDAD DE TRATAMIENTO DEL DOLOR S.A.S. - UNIDOLOR</t>
+  </si>
+  <si>
+    <t>ARISTIZABAL FRANCO LTDA</t>
+  </si>
+  <si>
+    <t>EMPRESA SOCIAL DEL ESTADO HOSPITAL SANTA TERESITA DE PACORA</t>
+  </si>
+  <si>
+    <t>HOSPITAL LOCAL DE GUAMAL PRIMER NIVEL ESE</t>
+  </si>
+  <si>
+    <t>13.04.2026</t>
+  </si>
+  <si>
+    <t>I TRIMESTRE</t>
   </si>
 </sst>
 </file>
@@ -141,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -150,12 +192,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -180,6 +216,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Formulario"/>
@@ -3512,7 +3549,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0157F28-2581-40E8-9FC3-C11753EC3402}">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -3522,7 +3559,7 @@
     <col min="5" max="16384" width="11.42578125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3535,74 +3572,150 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
     </row>
-    <row r="2" spans="1:5" ht="60" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="5" t="s">
+    </row>
+    <row r="4" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="2" t="s">
+    </row>
+    <row r="5" spans="1:4" ht="105" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="75" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>18</v>
-      </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="3"/>
+    <row r="8" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="3"/>
+    <row r="9" spans="1:4" ht="105" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="3"/>
+    <row r="10" spans="1:4" ht="75" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="3"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="3"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="3"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="3"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="3"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="3"/>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3617,7 +3730,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1">
         <v>830005028</v>
@@ -3627,18 +3740,18 @@
         <v>0815-2025</v>
       </c>
       <c r="D1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" t="s">
         <v>6</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>7</v>
-      </c>
-      <c r="F1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2">
         <v>900521595</v>
@@ -3648,18 +3761,18 @@
         <v>0639-2024</v>
       </c>
       <c r="D2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" t="s">
         <v>6</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3">
         <v>900685235</v>
@@ -3669,18 +3782,18 @@
         <v>0835-2021</v>
       </c>
       <c r="D3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
         <v>6</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>7</v>
-      </c>
-      <c r="F3" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>846001425</v>
@@ -3690,18 +3803,18 @@
         <v>0952-2024</v>
       </c>
       <c r="D4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" t="s">
         <v>6</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>892000458</v>
@@ -3711,18 +3824,18 @@
         <v>0618-2025</v>
       </c>
       <c r="D5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" t="s">
         <v>6</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>7</v>
-      </c>
-      <c r="F5" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6">
         <v>845000038</v>
@@ -3732,18 +3845,18 @@
         <v>0791-2024</v>
       </c>
       <c r="D6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" t="s">
         <v>6</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>7</v>
-      </c>
-      <c r="F6" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7">
         <v>800065396</v>
@@ -3753,18 +3866,18 @@
         <v>0700-2024</v>
       </c>
       <c r="D7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" t="s">
         <v>6</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>7</v>
-      </c>
-      <c r="F7" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8">
         <v>900526144</v>
@@ -3774,13 +3887,13 @@
         <v>0723-2024</v>
       </c>
       <c r="D8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" t="s">
         <v>6</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/SCRIPT_PDFS/SCRIPS_DOCUMENTADOS/PDF CALIDAD/IPS SIN MEDICION/indicadores sin medion.xlsx
+++ b/SCRIPT_PDFS/SCRIPS_DOCUMENTADOS/PDF CALIDAD/IPS SIN MEDICION/indicadores sin medion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Usuariios\prueba\Automatizaciones\SCRIPT_PDFS\SCRIPS_DOCUMENTADOS\PDF CALIDAD\IPS SIN MEDICION\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A5E755E-66DE-4BDE-882C-12DFA3B7123B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EA30861-EA29-44D0-BAD9-8A64DCA971AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="1080" windowWidth="21600" windowHeight="11295" xr2:uid="{7F76B178-B5D4-4098-B7B9-F39AFCAC640C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7F76B178-B5D4-4098-B7B9-F39AFCAC640C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -141,10 +141,10 @@
     <t>HOSPITAL LOCAL DE GUAMAL PRIMER NIVEL ESE</t>
   </si>
   <si>
-    <t>13.04.2026</t>
+    <t>I TRIMESTRE</t>
   </si>
   <si>
-    <t>I TRIMESTRE</t>
+    <t>20.04.2026</t>
   </si>
 </sst>
 </file>
@@ -3575,10 +3575,10 @@
     </row>
     <row r="2" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>24</v>
@@ -3589,10 +3589,10 @@
     </row>
     <row r="3" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>25</v>
@@ -3603,10 +3603,10 @@
     </row>
     <row r="4" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>26</v>
@@ -3617,10 +3617,10 @@
     </row>
     <row r="5" spans="1:4" ht="105" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>27</v>
@@ -3631,10 +3631,10 @@
     </row>
     <row r="6" spans="1:4" ht="90" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>28</v>
@@ -3645,10 +3645,10 @@
     </row>
     <row r="7" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -3659,10 +3659,10 @@
     </row>
     <row r="8" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>30</v>
@@ -3673,10 +3673,10 @@
     </row>
     <row r="9" spans="1:4" ht="105" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>31</v>
@@ -3687,10 +3687,10 @@
     </row>
     <row r="10" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>32</v>

--- a/SCRIPT_PDFS/SCRIPS_DOCUMENTADOS/PDF CALIDAD/IPS SIN MEDICION/indicadores sin medion.xlsx
+++ b/SCRIPT_PDFS/SCRIPS_DOCUMENTADOS/PDF CALIDAD/IPS SIN MEDICION/indicadores sin medion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Usuariios\prueba\Automatizaciones\SCRIPT_PDFS\SCRIPS_DOCUMENTADOS\PDF CALIDAD\IPS SIN MEDICION\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AGS\DESARROLLO\GITHUB\Automatizaciones\SCRIPT_PDFS\SCRIPS_DOCUMENTADOS\PDF CALIDAD\IPS SIN MEDICION\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EA30861-EA29-44D0-BAD9-8A64DCA971AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF24D428-8DEC-4E7D-AD13-B66B053B2582}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7F76B178-B5D4-4098-B7B9-F39AFCAC640C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{7F76B178-B5D4-4098-B7B9-F39AFCAC640C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -31,16 +31,17 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="61">
   <si>
     <t>campoa</t>
   </si>
@@ -87,64 +88,142 @@
     <t>NUEVA SALUD INTEGRAL IPS SAS</t>
   </si>
   <si>
-    <t>0758-2021</t>
-  </si>
-  <si>
-    <t>0050-2024</t>
-  </si>
-  <si>
-    <t>0726-2024</t>
-  </si>
-  <si>
-    <t>0890-2024</t>
-  </si>
-  <si>
-    <t>0040-2025</t>
-  </si>
-  <si>
-    <t>0138-2025</t>
-  </si>
-  <si>
-    <t>0606-2025</t>
-  </si>
-  <si>
-    <t>0615-2025</t>
-  </si>
-  <si>
-    <t>0827-2021</t>
-  </si>
-  <si>
-    <t>GRUPO PREFERENCIAL SANAR IPS S.A.S.</t>
-  </si>
-  <si>
-    <t>CENTRO MEDICO DEPORTIVO MET SAS</t>
-  </si>
-  <si>
-    <t>IMÁGENES Y ESPECIALIDADES S.A.S. – IMESS S.A.S</t>
-  </si>
-  <si>
-    <t>EMPRESA SOCIAL DEL ESTADO HOSPITAL MUNICIPAL DE EL DORADO</t>
-  </si>
-  <si>
-    <t>E.S.E HOSPITAL HABACUC CALDERON CARMEN DE CARUPA</t>
-  </si>
-  <si>
-    <t>UNIDAD DE TRATAMIENTO DEL DOLOR S.A.S. - UNIDOLOR</t>
-  </si>
-  <si>
-    <t>ARISTIZABAL FRANCO LTDA</t>
-  </si>
-  <si>
-    <t>EMPRESA SOCIAL DEL ESTADO HOSPITAL SANTA TERESITA DE PACORA</t>
-  </si>
-  <si>
-    <t>HOSPITAL LOCAL DE GUAMAL PRIMER NIVEL ESE</t>
-  </si>
-  <si>
     <t>I TRIMESTRE</t>
   </si>
   <si>
     <t>20.04.2026</t>
+  </si>
+  <si>
+    <t>0639-2024</t>
+  </si>
+  <si>
+    <t>0904-2024</t>
+  </si>
+  <si>
+    <t>0859-2021</t>
+  </si>
+  <si>
+    <t>0916-2021</t>
+  </si>
+  <si>
+    <t>0037-2025</t>
+  </si>
+  <si>
+    <t>0381-2022</t>
+  </si>
+  <si>
+    <t>0295-2022</t>
+  </si>
+  <si>
+    <t>0292-2022</t>
+  </si>
+  <si>
+    <t>0296-2022</t>
+  </si>
+  <si>
+    <t>0791-2024</t>
+  </si>
+  <si>
+    <t>0613-2023</t>
+  </si>
+  <si>
+    <t>0513-2023</t>
+  </si>
+  <si>
+    <t>0675-2025</t>
+  </si>
+  <si>
+    <t>0817-2024</t>
+  </si>
+  <si>
+    <t>0796-2025</t>
+  </si>
+  <si>
+    <t>0296-2025</t>
+  </si>
+  <si>
+    <t>0611-2025</t>
+  </si>
+  <si>
+    <t>0276-2022</t>
+  </si>
+  <si>
+    <t>0474-2022</t>
+  </si>
+  <si>
+    <t>0273-2022</t>
+  </si>
+  <si>
+    <t>0546-2023</t>
+  </si>
+  <si>
+    <t>0757-2023</t>
+  </si>
+  <si>
+    <t>CENTRO OFTALMOLÓGICO OCULASER S.A.S. - COFOLA S.A.S.</t>
+  </si>
+  <si>
+    <t>EMPRESA SOCIAL DEL ESTADO CENTRO DE SALUD VENTAQUEMADA</t>
+  </si>
+  <si>
+    <t>HOSPITAL SAN JOSE DE VITERBO</t>
+  </si>
+  <si>
+    <t>EMPRESA SOCIAL DEL ESTADO HOSPITAL SAN VICENTE DE RAMIRIQUÍ</t>
+  </si>
+  <si>
+    <t>E.S.E CENTRO DE SALUD CUCUNUBA</t>
+  </si>
+  <si>
+    <t>INVERSIONES MEREZ S.A.S</t>
+  </si>
+  <si>
+    <t>CONSORCIO CLINICA EMMANUEL</t>
+  </si>
+  <si>
+    <t>ESE RAFAEL TOVAR POVEDA</t>
+  </si>
+  <si>
+    <t>ESE HOSPITAL MALVINAS HECTOR OROZCO OROZCO</t>
+  </si>
+  <si>
+    <t>EMPRESA SOCIAL DEL ESTADO SAN ANTONIO</t>
+  </si>
+  <si>
+    <t>UNIVERSIDAD NACIONAL DE COLOMBIA</t>
+  </si>
+  <si>
+    <t>SUBRED INTEGRADA DE SERVICIOS DE SALUD SUR OCCIDENTE E.S.E</t>
+  </si>
+  <si>
+    <t>HOSPITAL SAN JOSE DE AGUADAS EMPRESA SOCIAL DEL ESTADO</t>
+  </si>
+  <si>
+    <t>CLINICA JUAN N CORPAS LTDA</t>
+  </si>
+  <si>
+    <t>ADMINISTRADORA CLINICA LA COLINA S.A.S.</t>
+  </si>
+  <si>
+    <t>EMPRESA SOCIAL DEL ESTADO HOSPITAL JOSE MARIA HERNANDEZ</t>
+  </si>
+  <si>
+    <t>EMPRESA SOCIAL DEL ESTADO HOSPITAL LA MISERICORDIA DE CALARCA</t>
+  </si>
+  <si>
+    <t>ESE DEPARTAMENTAL DE PRIMER NIVEL MORENO Y CLAVIJO</t>
+  </si>
+  <si>
+    <t>CLÍNICA LA SAGRADA FAMILIA S.A.S</t>
+  </si>
+  <si>
+    <t>BALANCE SALUD S.A.S</t>
+  </si>
+  <si>
+    <t>EMPRESA SOCIAL DEL ESTADO DEL DEPARTAMENTO DEL META ESE SOLUCION SALUD</t>
+  </si>
+  <si>
+    <t>GENCELL PHARMA S.A.S</t>
   </si>
 </sst>
 </file>
@@ -154,7 +233,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -162,16 +241,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="Century Gothic"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -179,11 +269,57 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -193,6 +329,21 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -212,12 +363,8 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Formulario"/>
       <sheetName val="Listas"/>
@@ -3549,17 +3696,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0157F28-2581-40E8-9FC3-C11753EC3402}">
-  <dimension ref="A1:D16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D23"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.375" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="29.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" style="1"/>
-    <col min="5" max="16384" width="11.42578125" style="2"/>
+    <col min="1" max="1" width="29.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.375" style="1"/>
+    <col min="5" max="16384" width="11.375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3573,149 +3720,313 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" s="1" t="s">
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="C20" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="3" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" s="1" t="s">
+    <row r="21" spans="1:4">
+      <c r="A21" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="B21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="4" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>17</v>
+    <row r="22" spans="1:4">
+      <c r="A22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="105" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="90" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="75" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="105" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="75" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="3"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="3"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="3"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="3"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="3"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="3"/>
+    <row r="23" spans="1:4">
+      <c r="A23" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>38</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3726,9 +4037,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B99E714-8989-4E86-A304-F9BF3A7AA005}">
   <dimension ref="A1:F8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -3749,7 +4060,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -3770,7 +4081,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -3791,7 +4102,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -3812,7 +4123,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -3833,7 +4144,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -3854,7 +4165,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -3875,7 +4186,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
         <v>14</v>
       </c>
